--- a/experimental/attention/kv_cache_turbo_quant/task_submission/4.1 内存自验证报告.xlsx
+++ b/experimental/attention/kv_cache_turbo_quant/task_submission/4.1 内存自验证报告.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="内存自验证" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内存自验证" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,15 +527,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>workspace 规模（申报值）</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>t2048 档 33.88MB（= LibApi 固定段 16MB + 2×8192KB 行缓冲 + 65KB 行范数）；decode_b1 16.02MB、decode_b64 16.63MB。行缓冲按「阶段互斥」别名：residual→unit 缓冲、projection→rotated 缓冲（数值等价，逐位回归通过）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>任务书未提出内存指标要求，故无内存专项测试项与测试数据。</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>本轮附带改动：行缓冲别名化把 t2048 档 workspace 从 50.92MB 降到 33.88MB（-33%），同时使每次调用的 aclrtMalloc 落入运行时内存池快路径（≤35MB 档 ~2µs，50.92MB 档 ~53µs）。依据见 docs/evidence/repro/2026-09-30_kctq_bitexact_reverse/alias/README.md 与 alias/wsbytes_cost.log。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A7:B7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
